--- a/tools/importer/reports/import-detail-with-tabs.report.xlsx
+++ b/tools/importer/reports/import-detail-with-tabs.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="91">
   <si>
     <t>_reportFile</t>
   </si>
@@ -59,6 +59,231 @@
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/bali-surf-camp.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/beervana-portland.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/beervana-portland</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:18:02.641Z</t>
+  </si>
+  <si>
+    <t>Beervana in Portland</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/beervana-portland.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/climbing-new-zealand.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/climbing-new-zealand</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:05:12.735Z</t>
+  </si>
+  <si>
+    <t>Climbing New Zealand</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/climbing-new-zealand.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/colorado-rock-climbing.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/colorado-rock-climbing</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:18:08.572Z</t>
+  </si>
+  <si>
+    <t>Colorado Rock Climbing</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/colorado-rock-climbing.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-southern-utah.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-southern-utah</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:18:13.125Z</t>
+  </si>
+  <si>
+    <t>Cycling Southern Utah</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/cycling-southern-utah.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-tuscany.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-tuscany</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:18:18.845Z</t>
+  </si>
+  <si>
+    <t>Cycling Tuscany</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/cycling-tuscany.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/downhill-skiing-wyoming.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/downhill-skiing-wyoming</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:18:25.291Z</t>
+  </si>
+  <si>
+    <t>Downhill Skiing Wyoming</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/downhill-skiing-wyoming.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/gastronomic-marais-tour.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/gastronomic-marais-tour</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:18:31.484Z</t>
+  </si>
+  <si>
+    <t>Gastronomic Marais Tour</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/gastronomic-marais-tour.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/napa-wine-tasting.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/napa-wine-tasting</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:05:23.609Z</t>
+  </si>
+  <si>
+    <t>Napa Wine Tasting</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/napa-wine-tasting.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/riverside-camping-australia.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/riverside-camping-australia</t>
+  </si>
+  <si>
+    <t>2026-09-07T02:13:12.220Z</t>
+  </si>
+  <si>
+    <t>Riverside Camping</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/riverside-camping-australia.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/ski-touring-mont-blanc.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/ski-touring-mont-blanc</t>
+  </si>
+  <si>
+    <t>2026-09-07T02:13:16.826Z</t>
+  </si>
+  <si>
+    <t>Ski Touring Mont Blanc</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/ski-touring-mont-blanc.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/surf-camp-costa-rica.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/surf-camp-costa-rica</t>
+  </si>
+  <si>
+    <t>2026-09-07T02:13:23.014Z</t>
+  </si>
+  <si>
+    <t>Surf Camp in Costa Rica</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/surf-camp-costa-rica.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/tahoe-skiing.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/tahoe-skiing</t>
+  </si>
+  <si>
+    <t>2026-09-07T01:05:17.225Z</t>
+  </si>
+  <si>
+    <t>Tahoe Skiing</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/tahoe-skiing.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/west-coast-cycling.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/west-coast-cycling</t>
+  </si>
+  <si>
+    <t>2026-09-07T02:13:27.045Z</t>
+  </si>
+  <si>
+    <t>West Coast Cycling</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/west-coast-cycling.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/whistler-mountain-biking.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/whistler-mountain-biking</t>
+  </si>
+  <si>
+    <t>2026-09-07T02:13:32.333Z</t>
+  </si>
+  <si>
+    <t>Whistler Mountain Biking</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/whistler-mountain-biking.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/yosemite-backpacking.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/yosemite-backpacking</t>
+  </si>
+  <si>
+    <t>2026-09-07T02:13:38.852Z</t>
+  </si>
+  <si>
+    <t>Yosemite Backpacking</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/yosemite-backpacking.html</t>
   </si>
 </sst>
 </file>
@@ -447,15 +672,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="6" max="7" width="26" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -511,6 +734,396 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
